--- a/videos/001_sns_investment_scam/image_generation_worklist.xlsx
+++ b/videos/001_sns_investment_scam/image_generation_worklist.xlsx
@@ -49,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,28 +58,63 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
       <top style="medium">
         <color rgb="00444444"/>
       </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,17 +481,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="100" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="100" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,20 +518,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>reference_sheet_files</t>
+          <t>キャラクターシート</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>ロケーションシート</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>image_prompt</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>生成済み</t>
         </is>
@@ -520,356 +561,396 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting alone in a dark living room at midnight, face lit only by a smartphone screen, expression of worry and disbelief, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>001-02</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, close-up on his hand repeatedly swiping and tapping a smartphone screen in the dark, tense fingers, faint glow reflecting off his glasses, low-key desaturated ominous lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>地の文に場所描写なし（ロケーション判定不可）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>001-03</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, extreme close-up on his glasses reflecting a faint glowing upward line graph from the phone screen, glow with no legible content, low-key desaturated ominous lighting, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>地の文に場所描写なし（ロケーション判定不可）</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>001-04</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, extreme close-up on his exhausted face frozen in disbelief, phone glow casting harsh shadows across his features, low-key desaturated ominous lighting, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>地の文に場所描写なし（ロケーション判定不可）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>001-05</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, medium shot of his hand resting beside a closed retirement payout envelope and a small framed photo of his former company on a low wooden table, dim smartphone glow nearby, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>001-06</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, symbolic wide shot of faint glowing particles dissolving and drifting away from the smartphone light into the surrounding darkness, low-key desaturated ominous lighting, wide symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>地の文に場所描写なし（ロケーション判定不可）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>001-07</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>hook_ending_glimpse</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting with head down and shoulders slumped on a floor cushion, smartphone dimly glowing beside him on the tatami floor, staring into the darkness lost in thought, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>002-01</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, standing confidently with arms crossed, self-assured expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, warm, natural saturation, soft daylight, portrait, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>002-02</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, standing beside a shelf with family photos and small plants, looking proudly at an old framed photo of his small parts-processing company from decades ago, a nostalgic confident smile, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, warm, natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>002-03</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, P2_miwako.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png
+P2_miwako.png</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting together at the low wooden table with his wife, beside him a Japanese woman in her late 50s, dark hair with visible grey streaks at the temples, soft lavender knit cardigan, both looking peaceful and content, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, warm, natural saturation, soft daylight, two shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>002-04</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, close-up on his confident face mid-gesture as if asserting an opinion, a slightly prideful smile, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, warm, natural saturation, soft daylight, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>003</t>
@@ -888,306 +969,357 @@
       <c r="D13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, P2_miwako.png, LOC01_living_room.png</t>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png
+P2_miwako.png</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, receiving a cup of coffee from his wife in the morning, a calm quiet moment, beside him a Japanese woman in her late 50s, dark hair with visible grey streaks at the temples, soft lavender knit cardigan, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, warm, natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>003-02</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting at the low wooden table watching the evening news with a thoughtful expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, dim warm home lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>003-03</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting at the low wooden table on the tatami floor at night looking at a bank passbook with a faintly anxious expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, dim warm home lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>003-04</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>daily_life</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, close-up on his hand scrolling through economic news on his smartphone late at night, his finger pausing thoughtfully, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, dim warm home lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>004-01</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>a smartphone held in the hand of a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, the screen glowing with a fake investment advertisement featuring a smiling celebrity investor portrait and a fake verified checkmark badge, his tempted face softly out of focus behind, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>004-02</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, a flicker of suspicion crossing his face while looking at his smartphone screen, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>004-03</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his suspicious frown softening into a self-assured smile as he rationalizes to himself while looking at his smartphone, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>004-04</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his thumb tapping a link on his smartphone screen, the screen glowing as it transitions to a messaging app invitation, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>004-05</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his finger decisively tapping a registration button on his smartphone without hesitation, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>004-06</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his laptop sitting closed and untouched on the low wooden table beside him, symbolizing the official verification he never performed, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, wide symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1208,370 +1340,432 @@
       <c r="D23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, watching a smartphone showing a crowded group chat full of profit screenshots and charts, a growing greedy smile on his face, screen glow on his face, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>005-02</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, extreme close-up on his eyes reflecting a glowing rising balance graph on his phone screen, glow with no legible content, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>005-03</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his thumb tapping a withdrawal request button on his smartphone, a hopeful cautious expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>005-04</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, a look of stunned surprised relief as he checks a bank notification on his phone confirming money has arrived, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>005-05</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his finger decisively tapping to transfer a large sum on his smartphone, a determined committed expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>005-06</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting at the low wooden table late in the evening, absorbed and satisfied while watching the growing numbers on his phone screen, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>006-01</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting alone at the low wooden table late at night, staring at his smartphone with a boastful proud smile at the growing unrealized profit on screen, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>006-02</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, P2_miwako.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png
+P2_miwako.png</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, in their tatami living room at night irritably waving off his worried wife, beside him a Japanese woman in her late 50s, dark hair with visible grey streaks at the temples, soft lavender knit cardigan, looking anxious and hesitant, tension between them, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, two shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>006-03</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, a flicker of excitement on his face as a message notification glows on his smartphone screen, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>006-04</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting at the low wooden table with a retirement payout envelope in front of him, a contemplative tempted expression as he looks between the envelope and his smartphone, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>006-05</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his finger decisively tapping to transfer a large lump sum on his smartphone late at night, a resolute determined expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>006-06</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>misjudgment_accumulation</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, P2_miwako.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png
+P2_miwako.png</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, completely absorbed in his smartphone in the foreground, a Japanese woman in her late 50s, dark hair with visible grey streaks at the temples, soft lavender knit cardigan, softly out of focus and turned away in the background, symbolizing her forgotten warning, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, gradually cooler tones, mild desaturation as mistakes accumulate, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1592,542 +1786,615 @@
       <c r="D35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, walking into the bank branch holding a passbook and a personal seal, a determined expression, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>007-02</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>a young Japanese male bank teller in a navy uniform cautiously questioning an impatient elderly customer at a modern glass-partitioned bank counter in an open airy interior, the customer a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, waving off the warning with a proud irritated expression, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>visual_cast未登録の脇役「銀行員」が登場（シート参照対象外）</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>007-03</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>LOC02_bank_branch.png</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>a young Japanese male bank teller in a navy uniform, a look of quiet concern crossing his face as he carefully chooses his words, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>visual_cast未登録の脇役「銀行員」が登場（シート参照対象外）</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>007-04</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, extreme close-up on his irritated proud expression as he dismisses the teller's warning, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>007-05</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>LOC02_bank_branch.png</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>a young Japanese male bank teller in a navy uniform, close-up on his hands processing transfer documents at the counter with a resigned expression, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>visual_cast未登録の脇役「銀行員」が登場（シート参照対象外）</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>007-06</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>LOC02_bank_branch.png</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>a symbolic wide shot of faint glowing light streaming out from a bank counter toward an unknown distant point, representing money flowing away, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, wide symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>007-07</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, receiving a transfer receipt at the counter with a proud satisfied expression, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>007-08</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, walking away from the counter with a proud upright posture, unaware of what he has missed, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, cold, heavily desaturated, low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>008-01</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, checking his smartphone with a satisfied smile as the balance keeps rising, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>008-02</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his thumb casually tapping a withdrawal request button on his smartphone, a relaxed routine expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>008-03</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, repeatedly checking his smartphone with growing worry as no money arrives, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>008-04</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, a shocked confused expression reading an unfamiliar message glowing on his smartphone screen, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>008-05</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, extreme close-up on his face as a cold dawning dread spreads across his features, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, extreme close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>008-06</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, his hand hesitating then reluctantly tapping to transfer more money on his smartphone, a conflicted troubled expression, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>008-07</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, staring at his silent smartphone waiting for a reply that never comes, a growing sense of unease, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>008-08</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D50" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, a devastated expression staring at his smartphone screen glowing with a single ominous blank notification, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>008-09</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>crisis_regret</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="D51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, sitting in frozen shock staring at his smartphone showing a blank empty error screen, an expression of despair and disbelief, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, cold, heavily desaturated, low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2148,338 +2415,358 @@
       <c r="D52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>a clean informational illustration of a laptop screen showing an official financial regulator's registered-business list rendered as rows of plain placeholder bars instead of readable text, a magnifying glass over a search field, calm trustworthy mood, neutral even lighting, high clarity, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>009-02</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>a clean informational illustration, close-up detail on a magnifying glass hovering over a search field on a laptop screen, plain placeholder bars instead of readable text, calm trustworthy mood, neutral even lighting, high clarity, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>009-03</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, P2_miwako.png, LOC01_living_room.png</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png
+P2_miwako.png</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_living_room.png</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>a small stylized flashback vignette of a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, looking at a smartphone advertisement late at night, a warm traditional Japanese living room, tatami mat flooring, wooden sliding shoji doors, low wooden table, warm-toned lighting, family photos and small plants on a shelf, neutral, even lighting, high clarity, soft vignette recap framing, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>009-04</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>P1_fujita_kenichi.png, LOC02_bank_branch.png</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>P1_fujita_kenichi.png</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_bank_branch.png</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>a small stylized flashback vignette of a Japanese man in his early 60s, short greying receding hair, thin-framed glasses, beige cardigan over a pale collared shirt, average build, standing at a bank counter that morning, a modern Japanese bank branch interior, glass partition counters, bright clean lighting, contemporary furniture, open airy layout, neutral, even lighting, high clarity, soft vignette recap framing, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>009-05</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>a symbolic editorial illustration of a single path splitting into two diverging roads, one leading toward a bright open destination and the other fading into darkness, representing a few minutes of unmade effort deciding the fork in the road, calm trustworthy mood, neutral even lighting, high clarity, wide symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>010-01</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>a conceptual illustration of overconfidence bias, a human head silhouette with a concealed blind spot, an elderly Japanese man confidently walking toward a hidden trap, neutral even lighting, high clarity, symbolic editorial composition, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>010-02</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n">
+      <c r="D58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>a conceptual illustration, close-up detail on a human head silhouette with a shadowed concealed blind spot at its center, neutral even lighting, high clarity, symbolic editorial composition, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>010-03</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n">
+      <c r="D59" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>a conceptual illustration, a stack of abstract achievement and experience symbols casting a long overconfident shadow behind a silhouetted elderly figure, neutral even lighting, high clarity, symbolic editorial composition, wide symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>010-04</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D60" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>a conceptual illustration of a small glowing key turning successfully in a lock, symbolizing a single small deliberate success building false trust, neutral even lighting, high clarity, symbolic editorial composition, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>010-05</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n">
+      <c r="D61" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="8" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>a conceptual illustration of a symbolic gate quietly closing, representing the moment a person stops doubting, neutral even lighting, high clarity, symbolic editorial composition, medium symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>010-06</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n">
+      <c r="D62" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>a conceptual illustration of two gentle silhouettes, one reaching a hand toward the other in quiet concern, symbolizing listening to a family member's warning, neutral even lighting, high clarity, symbolic editorial composition, medium symbolic shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2500,50 +2787,52 @@
       <c r="D63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>a clean checklist infographic with five empty checkboxes arranged vertically with simple icons beside each, senior-friendly simple layout, calm neutral tones, high clarity, flat design, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>011-02</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>checklist</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>a clean checklist infographic, close-up detail on the five simple icons beside each empty checkbox, senior-friendly simple layout, calm neutral tones, high clarity, flat design, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>抽象図解のためキャラクター/ロケーションのシート参照は不要</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
